--- a/descargas/registro-jornada.xlsx
+++ b/descargas/registro-jornada.xlsx
@@ -1020,7 +1020,7 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>Escribe las horas como 9:00. Rellena solo las celdas amarillas. Modelo orientativo de calculalotuyo.es. Revisa tu convenio colectivo, que puede mejorar lo que dice la ley.</t>
+          <t>Escribe las horas como 9:00. Rellena solo las celdas amarillas.</t>
         </is>
       </c>
     </row>
